--- a/reports/一级子公司A_利润表_2025-03.xlsx
+++ b/reports/一级子公司A_利润表_2025-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>171246787</v>
+        <v>174600630</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166865299</v>
+        <v>166374172</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>460202004</v>
+        <v>459671421</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>677954</v>
+        <v>682434</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1876959</v>
+        <v>1876331</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>589044</v>
+        <v>592864</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1628035</v>
+        <v>1630717</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>497182</v>
+        <v>502649</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1376498</v>
+        <v>1383927</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>459485</v>
+        <v>462229</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1267420</v>
+        <v>1274407</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>248768</v>
+        <v>250874</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>687488</v>
+        <v>692814</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>200175</v>
+        <v>200311</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>551025</v>
+        <v>554011</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>168574179</v>
+        <v>171909269</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164192691</v>
+        <v>163682811</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84875233</v>
+        <v>84210383</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>233320653</v>
+        <v>233408254</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1556488</v>
+        <v>1542027</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4285190</v>
+        <v>4270844</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1406693</v>
+        <v>1392884</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3874219</v>
+        <v>3850420</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>74671801</v>
+        <v>74857171</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>206698008</v>
+        <v>206148258</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1608089</v>
+        <v>1599080</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4427794</v>
+        <v>4401332</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>697821</v>
+        <v>700473</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1932664</v>
+        <v>1927077</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2510341</v>
+        <v>2509839</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>6914364</v>
+        <v>6899568</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1095321</v>
+        <v>1104342</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3034302</v>
+        <v>3036512</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4291835</v>
+        <v>4321421</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>11862945</v>
+        <v>11887941</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89653</v>
+        <v>90472</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>269489</v>
+        <v>270817</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2290150</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>6317614</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1524415</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4211949</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>114136758</v>
+        <v>122141139</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>101984347</v>
+        <v>101754808</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>99873221</v>
+        <v>99664469</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>275539584</v>
+        <v>276127265</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2111126</v>
+        <v>2090339</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>5803643</v>
+        <v>5790100</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3780001</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>10459780</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1210054</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3343739</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>757221</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2089084</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>910376</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2507795</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>684280</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1882748</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>457153</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1257031</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>381596</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1049305</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1739943</v>
+        <v>1759009</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4820548</v>
+        <v>4840320</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1349656</v>
+        <v>1356959</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3723325</v>
+        <v>3738496</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1094166</v>
+        <v>1104788</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3026098</v>
+        <v>3048077</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8298471</v>
+        <v>8322685</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>22866313</v>
+        <v>22998797</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349357</v>
+        <v>350284</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1047160</v>
+        <v>969218</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>670474</v>
+        <v>668884</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2007095</v>
+        <v>2014112</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>761943</v>
+        <v>668884</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2279180</v>
+        <v>2014112</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90116</v>
+        <v>89571</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>269983</v>
+        <v>269692</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>340199</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1023180</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>661826</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1828446</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>227217</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>681209</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>170744</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>511101</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>285201</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>852718</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>952645</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2619391</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152665</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>456246</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114592</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>342735</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190969</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>571930</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133546</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>400606</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>95228</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>286127</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76019</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>228726</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56891</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>171319</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>54437421</v>
+        <v>52105213</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63059467</v>
+        <v>58385739</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>378003</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1045638</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94559</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>283908</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150174</v>
+        <v>149514</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>450949</v>
+        <v>448166</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>54287247</v>
+        <v>52333702</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5285894</v>
+        <v>5305227</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>15914806</v>
+        <v>15860282</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>49001353</v>
+        <v>47028475</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>49001353</v>
+        <v>47028475</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>49001353</v>
+        <v>47028475</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>49001353</v>
+        <v>47028475</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>49001353</v>
+        <v>47028475</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
